--- a/data/trans_camb/IP17-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 10,58</t>
+          <t>-6,0; 11,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 5,42</t>
+          <t>-10,02; 6,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 1,36</t>
+          <t>-13,33; 2,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 7,61</t>
+          <t>-7,47; 7,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 6,75</t>
+          <t>-8,01; 7,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 2,12</t>
+          <t>-13,56; 1,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 6,89</t>
+          <t>-3,84; 7,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 4,85</t>
+          <t>-6,79; 4,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -0,25</t>
+          <t>-11,07; 0,6</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 65,93</t>
+          <t>-24,45; 68,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 31,95</t>
+          <t>-41,48; 38,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 10,15</t>
+          <t>-55,64; 19,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 45,03</t>
+          <t>-30,51; 42,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,25; 39,05</t>
+          <t>-32,39; 44,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 11,55</t>
+          <t>-54,74; 10,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 38,23</t>
+          <t>-16,69; 39,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 26,03</t>
+          <t>-29,34; 27,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-48,36; -1,46</t>
+          <t>-47,1; 4,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 6,49</t>
+          <t>-6,79; 6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 8,9</t>
+          <t>-3,87; 9,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -1,25</t>
+          <t>-13,99; -1,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 7,48</t>
+          <t>-5,66; 7,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 5,9</t>
+          <t>-7,31; 5,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 3,63</t>
+          <t>-9,8; 3,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 5,22</t>
+          <t>-3,98; 5,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 5,37</t>
+          <t>-4,0; 5,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -0,35</t>
+          <t>-9,38; -0,11</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 30,98</t>
+          <t>-26,48; 32,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 44,79</t>
+          <t>-15,18; 45,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,2; -5,76</t>
+          <t>-53,56; -7,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 38,33</t>
+          <t>-21,67; 42,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 29,9</t>
+          <t>-27,73; 29,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 19,02</t>
+          <t>-37,2; 17,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 25,17</t>
+          <t>-15,95; 26,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 26,31</t>
+          <t>-15,93; 26,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,32; -0,16</t>
+          <t>-38,51; -0,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 11,45</t>
+          <t>-3,38; 10,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 9,4</t>
+          <t>-5,06; 9,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 4,79</t>
+          <t>-10,6; 4,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 10,4</t>
+          <t>-4,82; 10,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 2,94</t>
+          <t>-11,79; 3,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 2,14</t>
+          <t>-12,6; 2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 8,26</t>
+          <t>-1,87; 8,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 4,05</t>
+          <t>-6,52; 3,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 0,91</t>
+          <t>-10,19; 0,98</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 86,06</t>
+          <t>-18,11; 73,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 70,7</t>
+          <t>-23,97; 69,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 34,44</t>
+          <t>-54,57; 31,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 54,57</t>
+          <t>-18,3; 56,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,35; 15,81</t>
+          <t>-43,44; 17,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,66; 12,05</t>
+          <t>-49,57; 12,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 46,23</t>
+          <t>-8,53; 49,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 23,79</t>
+          <t>-27,59; 22,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 5,17</t>
+          <t>-46,37; 5,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 13,55</t>
+          <t>0,14; 13,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 6,47</t>
+          <t>-6,76; 6,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,78</t>
+          <t>-7,24; 5,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 4,14</t>
+          <t>-9,86; 3,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 1,93</t>
+          <t>-11,63; 1,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; -0,01</t>
+          <t>-14,69; -0,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,11</t>
+          <t>-3,25; 6,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 2,17</t>
+          <t>-7,29; 2,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 0,58</t>
+          <t>-9,59; 0,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 90,76</t>
+          <t>0,82; 89,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 43,11</t>
+          <t>-31,72; 46,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 39,09</t>
+          <t>-35,17; 35,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 22,01</t>
+          <t>-36,83; 18,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 9,8</t>
+          <t>-44,42; 7,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 0,58</t>
+          <t>-54,5; -3,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 38,7</t>
+          <t>-13,22; 35,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 12,52</t>
+          <t>-31,67; 11,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,4; 3,62</t>
+          <t>-40,78; 0,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 7,06</t>
+          <t>-0,03; 6,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,06</t>
+          <t>-2,53; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -0,61</t>
+          <t>-8,34; -0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,79</t>
+          <t>-3,24; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,63</t>
+          <t>-6,05; 0,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -1,81</t>
+          <t>-9,17; -2,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,32</t>
+          <t>-0,91; 4,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,75</t>
+          <t>-3,54; 1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -2,21</t>
+          <t>-7,31; -2,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 39,19</t>
+          <t>-0,15; 38,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 22,67</t>
+          <t>-12,08; 22,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,96; -3,16</t>
+          <t>-38,56; -3,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 17,95</t>
+          <t>-13,33; 18,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 3,17</t>
+          <t>-24,95; 3,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,68; -8,86</t>
+          <t>-36,66; -9,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 22,06</t>
+          <t>-3,93; 21,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 8,35</t>
+          <t>-15,55; 7,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,84; -11,36</t>
+          <t>-33,09; -12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 11,19</t>
+          <t>-4,29; 11,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 6,07</t>
+          <t>-10,15; 5,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 2,73</t>
+          <t>-13,07; 2,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 7,43</t>
+          <t>-7,08; 8,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 7,84</t>
+          <t>-7,85; 7,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 1,96</t>
+          <t>-13,27; 2,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,25</t>
+          <t>-4,68; 6,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,72</t>
+          <t>-6,72; 4,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 0,6</t>
+          <t>-10,8; -0,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 68,45</t>
+          <t>-18,69; 77,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 38,83</t>
+          <t>-40,54; 36,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,64; 19,17</t>
+          <t>-55,07; 13,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 42,63</t>
+          <t>-29,43; 50,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 44,97</t>
+          <t>-32,6; 44,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 10,41</t>
+          <t>-54,31; 14,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 39,89</t>
+          <t>-19,54; 38,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 27,97</t>
+          <t>-29,38; 22,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 4,74</t>
+          <t>-47,09; -0,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 6,15</t>
+          <t>-6,68; 6,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 9,13</t>
+          <t>-3,54; 8,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -1,46</t>
+          <t>-13,99; -1,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,83</t>
+          <t>-5,29; 7,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 5,63</t>
+          <t>-7,19; 5,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 3,19</t>
+          <t>-9,25; 3,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,46</t>
+          <t>-4,08; 5,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 5,44</t>
+          <t>-3,93; 5,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -0,11</t>
+          <t>-9,48; -0,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 32,01</t>
+          <t>-25,15; 30,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 45,4</t>
+          <t>-13,66; 45,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,56; -7,56</t>
+          <t>-53,98; -4,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 42,62</t>
+          <t>-20,44; 39,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 29,37</t>
+          <t>-27,9; 27,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 17,35</t>
+          <t>-36,15; 19,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 26,22</t>
+          <t>-16,41; 25,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 26,6</t>
+          <t>-16,12; 25,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,51; -0,33</t>
+          <t>-38,3; -3,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 10,27</t>
+          <t>-2,45; 11,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 9,17</t>
+          <t>-4,64; 9,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 4,63</t>
+          <t>-11,68; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 10,62</t>
+          <t>-4,37; 10,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 3,1</t>
+          <t>-11,56; 2,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 2,46</t>
+          <t>-13,18; 1,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 8,72</t>
+          <t>-1,92; 9,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 3,96</t>
+          <t>-6,17; 3,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 0,98</t>
+          <t>-10,32; 1,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 73,42</t>
+          <t>-11,81; 93,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 69,42</t>
+          <t>-22,72; 73,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 31,41</t>
+          <t>-57,82; 30,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 56,26</t>
+          <t>-16,47; 57,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 17,0</t>
+          <t>-43,0; 15,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 12,74</t>
+          <t>-49,95; 9,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 49,77</t>
+          <t>-8,56; 55,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 22,32</t>
+          <t>-27,7; 20,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 5,33</t>
+          <t>-45,94; 7,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 13,55</t>
+          <t>0,24; 13,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 6,92</t>
+          <t>-6,59; 6,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 5,48</t>
+          <t>-7,15; 5,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 3,6</t>
+          <t>-9,09; 4,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 1,45</t>
+          <t>-11,33; 1,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -0,65</t>
+          <t>-13,73; -0,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 6,64</t>
+          <t>-2,59; 6,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,08</t>
+          <t>-6,77; 2,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 0,06</t>
+          <t>-9,41; 0,02</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 89,95</t>
+          <t>-0,61; 93,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 46,42</t>
+          <t>-31,78; 45,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 35,95</t>
+          <t>-34,06; 35,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 18,93</t>
+          <t>-34,33; 20,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 7,95</t>
+          <t>-43,98; 9,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,5; -3,14</t>
+          <t>-53,07; -3,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 35,83</t>
+          <t>-11,85; 37,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 11,32</t>
+          <t>-30,01; 14,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 0,69</t>
+          <t>-40,38; 0,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,95</t>
+          <t>-0,0; 7,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,08</t>
+          <t>-2,5; 4,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -0,61</t>
+          <t>-8,27; -0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,78</t>
+          <t>-3,49; 3,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,76</t>
+          <t>-6,22; 0,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -2,06</t>
+          <t>-8,53; -1,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,15</t>
+          <t>-0,67; 4,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,51</t>
+          <t>-3,37; 1,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -2,41</t>
+          <t>-7,19; -2,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 38,51</t>
+          <t>0,04; 39,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 22,6</t>
+          <t>-11,5; 24,5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,56; -3,14</t>
+          <t>-38,79; -5,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 18,15</t>
+          <t>-14,77; 18,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 3,84</t>
+          <t>-26,01; 4,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; -9,59</t>
+          <t>-36,05; -8,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 21,08</t>
+          <t>-3,01; 22,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 7,63</t>
+          <t>-15,05; 7,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; -12,02</t>
+          <t>-32,64; -11,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,07</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,93</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,27</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,56</t>
+          <t>-6,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-5,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 11,67</t>
+          <t>-7,4; 7,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 5,99</t>
+          <t>-8,12; 6,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 2,43</t>
+          <t>-13,02; 2,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 8,04</t>
+          <t>-5,55; 10,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 7,49</t>
+          <t>-10,43; 5,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 2,45</t>
+          <t>-14,3; 1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,67</t>
+          <t>-4,23; 6,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 4,18</t>
+          <t>-6,45; 4,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -0,1</t>
+          <t>-11,03; -0,17</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-1,07%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-24,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>14,5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-11,19%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-28,17%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,07%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-26,48%</t>
+          <t>-30,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-27,18%</t>
+          <t>-27,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 77,45</t>
+          <t>-30,52; 45,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 36,29</t>
+          <t>-32,25; 39,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 13,47</t>
+          <t>-52,58; 14,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 50,48</t>
+          <t>-23,33; 65,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 44,52</t>
+          <t>-44,85; 31,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 14,15</t>
+          <t>-57,98; 8,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 38,38</t>
+          <t>-18,04; 38,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 22,74</t>
+          <t>-28,09; 26,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,09; -0,46</t>
+          <t>-47,66; -0,79</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,08</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,37</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,73</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-8,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>-5,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,04</t>
+          <t>-5,28; 7,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 8,87</t>
+          <t>-7,17; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -1,15</t>
+          <t>-8,82; 3,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,48</t>
+          <t>-7,01; 6,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,14</t>
+          <t>-4,53; 8,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 3,38</t>
+          <t>-14,75; -2,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,13</t>
+          <t>-4,12; 5,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 5,03</t>
+          <t>-4,0; 5,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; -0,88</t>
+          <t>-9,94; -0,59</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-4,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-14,97%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-0,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,28%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-33,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,78%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,35%</t>
+          <t>-36,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,22%</t>
+          <t>-24,46%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 30,78</t>
+          <t>-20,76; 38,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 45,89</t>
+          <t>-27,66; 29,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,98; -4,87</t>
+          <t>-35,19; 17,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 39,27</t>
+          <t>-26,22; 30,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 27,33</t>
+          <t>-17,55; 44,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 19,17</t>
+          <t>-56,06; -8,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 25,02</t>
+          <t>-17,01; 25,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 25,11</t>
+          <t>-16,02; 26,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,3; -3,76</t>
+          <t>-40,08; -2,53</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,79</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,05</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,55</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,21</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,36</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,62</t>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,55</t>
+          <t>-3,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 11,4</t>
+          <t>-4,45; 10,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 9,51</t>
+          <t>-11,59; 2,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 4,03</t>
+          <t>-12,16; 3,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 10,59</t>
+          <t>-3,07; 11,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 2,74</t>
+          <t>-3,77; 9,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,53</t>
+          <t>-9,38; 4,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 9,43</t>
+          <t>-1,7; 8,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 3,48</t>
+          <t>-5,78; 4,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 1,29</t>
+          <t>-8,62; 1,46</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-21,09%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>23,77%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>14,96%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-18,83%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,18%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,75%</t>
+          <t>-10,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-22,76%</t>
+          <t>-16,97%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 93,09</t>
+          <t>-16,8; 54,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 73,18</t>
+          <t>-43,35; 15,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 30,0</t>
+          <t>-46,95; 16,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 57,36</t>
+          <t>-15,67; 86,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 15,87</t>
+          <t>-18,86; 70,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 9,26</t>
+          <t>-44,31; 36,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 55,6</t>
+          <t>-8,25; 46,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 20,5</t>
+          <t>-25,22; 23,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 7,22</t>
+          <t>-37,52; 9,35</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,67</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,39</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,88</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,35</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,23</t>
+          <t>-4,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 13,73</t>
+          <t>-8,69; 4,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 6,52</t>
+          <t>-11,25; 1,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 5,68</t>
+          <t>-13,8; -0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 4,0</t>
+          <t>0,08; 13,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 1,79</t>
+          <t>-6,17; 6,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -0,74</t>
+          <t>-7,21; 5,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 6,8</t>
+          <t>-2,11; 7,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 2,58</t>
+          <t>-6,41; 2,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 0,02</t>
+          <t>-9,45; 0,36</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-10,35%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-21,15%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-33,22%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>37,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-6,15%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-10,35%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-21,15%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-31,83%</t>
+          <t>-6,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,71%</t>
+          <t>-21,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 93,16</t>
+          <t>-33,75; 22,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 45,87</t>
+          <t>-43,73; 9,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 35,4</t>
+          <t>-52,45; -1,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 20,2</t>
+          <t>0,53; 90,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 9,49</t>
+          <t>-29,72; 43,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,07; -3,97</t>
+          <t>-34,58; 39,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 37,89</t>
+          <t>-9,93; 38,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 14,35</t>
+          <t>-28,69; 12,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 0,28</t>
+          <t>-41,45; 1,09</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,03</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>-4,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-4,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 7,06</t>
+          <t>-3,38; 3,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,47</t>
+          <t>-6,38; 0,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,93</t>
+          <t>-8,71; -1,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,86</t>
+          <t>-0,3; 7,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,84</t>
+          <t>-2,89; 4,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -1,93</t>
+          <t>-7,68; -0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,35</t>
+          <t>-0,73; 4,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,41</t>
+          <t>-3,47; 1,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -2,22</t>
+          <t>-7,07; -2,23</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-11,92%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-22,44%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>17,15%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-23,14%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-11,92%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-22,88%</t>
+          <t>-22,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-22,8%</t>
+          <t>-22,37%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,04; 39,78</t>
+          <t>-13,77; 17,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 24,5</t>
+          <t>-26,02; 3,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,79; -5,31</t>
+          <t>-35,76; -7,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 18,8</t>
+          <t>-1,36; 39,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 4,05</t>
+          <t>-13,2; 22,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,05; -8,98</t>
+          <t>-35,76; -4,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 22,02</t>
+          <t>-3,07; 22,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 7,14</t>
+          <t>-15,78; 8,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,64; -11,15</t>
+          <t>-32,1; -11,21</t>
         </is>
       </c>
     </row>
